--- a/Metadata and header descriptions - NZ precipitation isotope database.xlsx
+++ b/Metadata and header descriptions - NZ precipitation isotope database.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niwa-my.sharepoint.com/personal/bruce_dudley_niwa_co_nz/Documents/Desktop/My_Science/publishing/36. Community isoscape note/Community isotope database manuscript/Files for submission/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nzies-my.sharepoint.com/personal/bruce_dudley_earthsciences_nz/Documents/Desktop/My_Science/publishing/36. Community isoscape note/Community isotope database manuscript/Files for submission/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{FC9F2AC1-FB3E-4FE3-B28F-D3501DBFED16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84BF21A5-A400-442E-B18A-0FC02FD65E20}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{FC9F2AC1-FB3E-4FE3-B28F-D3501DBFED16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50F5080C-4DE9-4BE1-A445-9AF942C326B3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{30575E4E-4C6E-403D-899F-0CA742198BC9}"/>
+    <workbookView xWindow="-28920" yWindow="-765" windowWidth="29040" windowHeight="15720" xr2:uid="{30575E4E-4C6E-403D-899F-0CA742198BC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
     <sheet name="HeaderDescriptions" sheetId="2" r:id="rId2"/>
+    <sheet name="Full_dailyplus_example" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Metadata!$A$1:$Q$245</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3000" uniqueCount="526">
   <si>
     <t>Site_Name</t>
   </si>
@@ -1582,6 +1583,75 @@
   </si>
   <si>
     <t>Yes or No</t>
+  </si>
+  <si>
+    <t>Institution</t>
+  </si>
+  <si>
+    <t>Notes 2</t>
+  </si>
+  <si>
+    <t>Hill AO 14</t>
+  </si>
+  <si>
+    <t>New snow collection</t>
+  </si>
+  <si>
+    <t>Collector was…</t>
+  </si>
+  <si>
+    <t>David Wright</t>
+  </si>
+  <si>
+    <t>Hill AO 58</t>
+  </si>
+  <si>
+    <t>Mike Lynds</t>
+  </si>
+  <si>
+    <t>melrose145</t>
+  </si>
+  <si>
+    <t>Collecting raingauge</t>
+  </si>
+  <si>
+    <t>melrose123</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B3.Christchurch</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>UC</t>
+  </si>
+  <si>
+    <t>Zane thesis</t>
+  </si>
+  <si>
+    <t>CSAS 1</t>
+  </si>
+  <si>
+    <t>Holman</t>
+  </si>
+  <si>
+    <t>Hill W-E APass - 29</t>
+  </si>
+  <si>
+    <t>Palmex</t>
+  </si>
+  <si>
+    <t>NW-S</t>
+  </si>
+  <si>
+    <t>Hill W-E Shef-45</t>
+  </si>
+  <si>
+    <t>South</t>
   </si>
 </sst>
 </file>
@@ -1996,7 +2066,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2088,6 +2158,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2430,6 +2503,8 @@
     <col min="1" max="1" width="36.33203125" customWidth="1"/>
     <col min="2" max="3" width="16.44140625" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="11" max="11" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="51.109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.5546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
@@ -15815,4 +15890,351 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{274670BD-CB1B-43FC-9D11-8BCA44BCA5C1}">
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E1" t="s">
+        <v>464</v>
+      </c>
+      <c r="F1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G1" t="s">
+        <v>468</v>
+      </c>
+      <c r="H1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I1" t="s">
+        <v>473</v>
+      </c>
+      <c r="J1" t="s">
+        <v>475</v>
+      </c>
+      <c r="K1" t="s">
+        <v>480</v>
+      </c>
+      <c r="L1" t="s">
+        <v>478</v>
+      </c>
+      <c r="M1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E2" s="1">
+        <v>44354</v>
+      </c>
+      <c r="F2" s="1">
+        <v>44384</v>
+      </c>
+      <c r="G2" s="37">
+        <v>0.375</v>
+      </c>
+      <c r="H2" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="J2" t="s">
+        <v>506</v>
+      </c>
+      <c r="K2">
+        <v>-24.14</v>
+      </c>
+      <c r="L2">
+        <v>-185.77</v>
+      </c>
+      <c r="M2" t="s">
+        <v>507</v>
+      </c>
+      <c r="N2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E3" s="1">
+        <v>44382</v>
+      </c>
+      <c r="F3" s="1">
+        <v>44384</v>
+      </c>
+      <c r="G3" s="37">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H3" s="38">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="J3" t="s">
+        <v>506</v>
+      </c>
+      <c r="K3">
+        <v>-21.78</v>
+      </c>
+      <c r="L3">
+        <v>-166.9</v>
+      </c>
+      <c r="M3" t="s">
+        <v>507</v>
+      </c>
+      <c r="N3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E4" s="1">
+        <v>42221</v>
+      </c>
+      <c r="F4" s="1">
+        <v>42224</v>
+      </c>
+      <c r="G4" s="39">
+        <v>0.375</v>
+      </c>
+      <c r="H4" s="37">
+        <v>0.375</v>
+      </c>
+      <c r="I4">
+        <v>5.6</v>
+      </c>
+      <c r="J4" t="s">
+        <v>512</v>
+      </c>
+      <c r="K4">
+        <v>-19.22</v>
+      </c>
+      <c r="L4">
+        <v>-136.91999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" t="s">
+        <v>513</v>
+      </c>
+      <c r="E5" s="1">
+        <v>42171</v>
+      </c>
+      <c r="F5" s="1">
+        <v>42174</v>
+      </c>
+      <c r="G5" s="39">
+        <v>0.375</v>
+      </c>
+      <c r="H5" s="37">
+        <v>0.375</v>
+      </c>
+      <c r="I5">
+        <v>44.9</v>
+      </c>
+      <c r="J5" t="s">
+        <v>512</v>
+      </c>
+      <c r="K5">
+        <v>-18.940000000000001</v>
+      </c>
+      <c r="L5">
+        <v>-139.63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>514</v>
+      </c>
+      <c r="B6" t="s">
+        <v>438</v>
+      </c>
+      <c r="C6" t="s">
+        <v>515</v>
+      </c>
+      <c r="D6" t="s">
+        <v>516</v>
+      </c>
+      <c r="E6" s="1">
+        <v>41675</v>
+      </c>
+      <c r="F6" s="1">
+        <v>41683</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>-4.16</v>
+      </c>
+      <c r="L6">
+        <v>-24.21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>517</v>
+      </c>
+      <c r="B7" t="s">
+        <v>518</v>
+      </c>
+      <c r="C7" t="s">
+        <v>368</v>
+      </c>
+      <c r="D7" t="s">
+        <v>519</v>
+      </c>
+      <c r="E7" s="1">
+        <v>45132</v>
+      </c>
+      <c r="F7" s="1">
+        <v>45155</v>
+      </c>
+      <c r="J7" t="s">
+        <v>520</v>
+      </c>
+      <c r="K7">
+        <v>-8.1300000000000008</v>
+      </c>
+      <c r="L7">
+        <v>-53.78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" t="s">
+        <v>521</v>
+      </c>
+      <c r="E8" s="1">
+        <v>44599</v>
+      </c>
+      <c r="F8" s="1">
+        <v>44606</v>
+      </c>
+      <c r="J8" t="s">
+        <v>522</v>
+      </c>
+      <c r="K8">
+        <v>-17.95</v>
+      </c>
+      <c r="L8">
+        <v>-136.34</v>
+      </c>
+      <c r="M8" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" t="s">
+        <v>524</v>
+      </c>
+      <c r="E9" s="1">
+        <v>44754</v>
+      </c>
+      <c r="F9" s="1">
+        <v>44760</v>
+      </c>
+      <c r="J9" t="s">
+        <v>522</v>
+      </c>
+      <c r="K9">
+        <v>-17.78</v>
+      </c>
+      <c r="L9">
+        <v>-134.93</v>
+      </c>
+      <c r="M9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>